--- a/Result/profitability/1799.xlsx
+++ b/Result/profitability/1799.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.52</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.01625</v>
+        <v>-0.02249999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>49.34875</v>
+        <v>48.4625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05125</v>
+        <v>0.06</v>
       </c>
       <c r="N3" t="n">
-        <v>49.46625</v>
+        <v>48.06375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.15</v>
+        <v>0.13875</v>
       </c>
       <c r="N4" t="n">
-        <v>48.56875</v>
+        <v>47.08374999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.18625</v>
+        <v>0.2225</v>
       </c>
       <c r="N5" t="n">
-        <v>47.6</v>
+        <v>48.05125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24125</v>
+        <v>0.2225</v>
       </c>
       <c r="N6" t="n">
-        <v>47.56</v>
+        <v>46.75875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2425</v>
+        <v>0.26</v>
       </c>
       <c r="N7" t="n">
-        <v>46.405</v>
+        <v>46.67749999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>0.29625</v>
+        <v>0.26375</v>
       </c>
       <c r="N8" t="n">
-        <v>46.015</v>
+        <v>44.90625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1648,7 +1648,7 @@
         <v>0.295</v>
       </c>
       <c r="N10" t="n">
-        <v>42.60250000000001</v>
+        <v>42.6025</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>-0.29</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07875000000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="N13" t="n">
         <v>39.2025</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>227</v>
+      </c>
+      <c r="D75" t="n">
+        <v>129</v>
+      </c>
+      <c r="E75" t="n">
+        <v>98</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.09375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-8.869999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.170053680981595</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7435897435897436</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.609999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09097782258064524</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
